--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0040.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0040.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Invalid difficulty index</t>
+          <t>Chỉ số độ khó không hợp lệ</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Result score count mismatch</t>
+          <t>Số điểm kết quả không khớp</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Invalid score</t>
+          <t>Điểm số không hợp lệ</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Failed to retrieve variable definition</t>
+          <t>Không lấy được định nghĩa biến số</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Invalid component data member type</t>
+          <t>Loại thành viên dữ liệu thành phần không hợp lệ</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Invalid component type</t>
+          <t>Loại thành phần không hợp lệ</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Prerequisite stage not completed</t>
+          <t>Giai đoạn Điều kiện tiên quyết chưa hoàn thành</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Nhắc nhở kết thúc sự kiện</t>
+          <t>Nhắc nhở Kết thúc Sự kiện</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Chính "Ánh Sao Từ Quá Khứ"</t>
+          <t>Hoàn thành Nhiệm vụ Chính "Ánh Sao Từ Những Ngày Xưa"</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1274,8 +1274,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Hoàn thành Đoạn Kết "
-Dưới bầu trời đêm tan rã"</t>
+          <t>Hoàn thành Đoạn Chuyển "Beneath a Melting Night Sky"</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1345,7 +1344,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Hoàn thành SkyArk 4 trong "Star Bouncing"</t>
+          <t>Hoàn thành SkyArk 4 trong "Nhảy Sao"</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1485,7 +1484,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Tham gia và hoàn thành tổng cộng 2 trận trong "Cubie Derby: Championship"</t>
+          <t>Tham gia và hoàn thành tổng cộng 2 trận đấu trong "Cubie Derby: Championship".</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1555,7 +1554,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Into the Dim</t>
+          <t>Vào Bóng Mờ</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1625,7 +1624,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Along the Trail</t>
+          <t>Dọc Theo Con Đường Mòn</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1695,7 +1694,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Reawakening Giọng nói</t>
+          <t>Tiếng Gọi Tái Sinh</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1765,7 +1764,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Return of Light</t>
+          <t>Sự trở lại của Ánh Sáng</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1835,7 +1834,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Into the Dim</t>
+          <t>Vào Bóng Mờ</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1905,7 +1904,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Along the Trail</t>
+          <t>Dọc Theo Con Đường Mòn</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1975,7 +1974,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Reawakening Giọng nói</t>
+          <t>Tiếng Gọi Tái Sinh</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2045,7 +2044,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Return of Light</t>
+          <t>Sự trở lại của Ánh Sáng</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2115,7 +2114,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Hoàn thành các đường đua Flight Track được chỉ định của Challenge Đường Đua Xe Máy</t>
+          <t>Hoàn thành các Đường Bay được chỉ định trong Thử Thách Xe Mô Tô</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2255,7 +2254,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Hoàn thành đường đua Fixed Track được chỉ định của Challenge Đường Đua Xe Máy</t>
+          <t>Hoàn thành Đường Đua Cố Định được chỉ định trong Thử Thách Xe Mô Tô</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2325,7 +2324,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Kích hoạt tần số do Hiyuki để lại một lần tại Dimmr Plains</t>
+          <t>Kích hoạt tần số Hiyuki để lại tại Đồng Bằng Dimmr một lần</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2395,7 +2394,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Nâng cấp trạm gốc lên Cấp 2</t>
+          <t>Nâng cấp Trạm Cơ Bản lên Cấp 2</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2465,7 +2464,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Exploration "Một Ngày Tuyệt Vời Để Bay"</t>
+          <t>Hoàn thành Nhiệm Vụ Thám Hiểm "Một Ngày Tuyệt Vời Để Bay Lượn"</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2535,7 +2534,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Exploration "Broken Dimmr Heart Nát"</t>
+          <t>Hoàn thành Nhiệm Vụ Thám Hiểm "Trái Tim Dimmu Vỡ Nát"</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2605,7 +2604,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Celebrate Denia's birthday with her</t>
+          <t>Cùng Denia tổ chức sinh nhật cho cô ấy</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2675,8 +2674,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Chính "
-Dưới bầu trời đêm tan rã"</t>
+          <t>Hoàn thành Nhiệm vụ Chính "Dưới Bầu Trời Đêm Tan Chảy"</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2746,7 +2744,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Play Lahai-Roi Blocks cùng Denia</t>
+          <t>Chơi Nhịp Điệu Lahai-Roi cùng Denia</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2816,7 +2814,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Witness Denia overcome her nightmare</t>
+          <t>Chứng kiến Denia vượt qua cơn ác mộng của mình</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2886,7 +2884,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Event không khả dụng</t>
+          <t>Sự kiện chưa khả dụng</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2956,7 +2954,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Event đã kết thúc</t>
+          <t>Sự kiện đã kết thúc</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3026,7 +3024,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Rewards Trở lại Thủy Triều (Tái diễn)</t>
+          <t>Phần Thưởng Người Trở Về Tái Ngộ Thủy Triều</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3236,7 +3234,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Soundless Prayer</t>
+          <t>Lời Cầu Nguyện Vô Âm</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3306,7 +3304,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Hiyuki - Original Trang phục</t>
+          <t>Bộ đồ Hiyuki - Trang phục gốc</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3376,7 +3374,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Decorated Shell</t>
+          <t>Vỏ Sò Được Trang Trí</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3446,7 +3444,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Denia - Original Trang phục</t>
+          <t>Denia - Trang Phục Nguyên Bản</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3516,7 +3514,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Sự trở lại của Solaris: Mùa Cộng tác</t>
+          <t>Sự Trở Lại Của Solaris: Mùa Cộng Tác</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3586,7 +3584,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Nhận Lunite</t>
+          <t>Nhận Đá Mặt Trăng</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3656,7 +3654,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Package from Jinzhou</t>
+          <t>Gói hàng từ Jinzhou</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3726,7 +3724,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Package from Rinascita</t>
+          <t>Gói hàng từ Rinascita</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3796,7 +3794,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Package from Lahai-Roi</t>
+          <t>Gói hàng từ Lahai-Roi</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3866,7 +3864,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Irreplaceable Memories</t>
+          <t>Những Ký Ức Không Thể Thay Thế</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3936,7 +3934,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Sự trở lại của Solaris: Event cộng tác giới hạn thời gian</t>
+          <t>Sự Trở Lại Của Solaris: Sự Kiện Cộng Tác Giới Hạn</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4006,7 +4004,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Golden Tide</t>
+          <t>Thủy Triều Vàng</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4076,7 +4074,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Mellow Shorelight</t>
+          <t>Ánh Sáng Bờ Biển Dịu Dàng</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4146,7 +4144,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Offshore Echoes</t>
+          <t>Tiếng Vọng Ngoài Khơi</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4216,7 +4214,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>I, Lahai-Roi</t>
+          <t>Ta, Lahai-Roi...</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4286,7 +4284,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Scorching Frost</t>
+          <t>Sương Giá Nóng Rực</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4356,7 +4354,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Spectrum of the Dark</t>
+          <t>Phổ Bóng Tối</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4426,7 +4424,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Supernova Launcher</t>
+          <t>Bệ Phóng Tinh Vân</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4496,7 +4494,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Hoàn thành Endless Galaxy Track 10 trong sự kiện "Star Bouncing"</t>
+          <t>Hoàn thành Đường Đua Endless Galaxy 10 trong sự kiện "Star Bouncing"</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4566,7 +4564,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Fantasy Weaver</t>
+          <t>Kẻ Dệt Ảo Ảnh</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4636,7 +4634,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Tidesong Once More</t>
+          <t>Khúc Ca Triều Lại Vang</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4706,7 +4704,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Event giới hạn thời gian "Quà Tặng Lễ Kỷ Niệm 2026"</t>
+          <t>Sự Kiện Hạn Chế Quà Tặng Đại Kỷ Niệm 2026</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4846,7 +4844,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Sự kiện "Vào Land Paradox"</t>
+          <t>"Sự kiện "Vào Vùng Đất Nghịch Lý""</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4916,7 +4914,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Ước Nguyện Trong Chuông</t>
+          <t>Điều Ước Trong Chuông</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4986,7 +4984,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Ánh Sao Từ Ngày Qua</t>
+          <t>Ánh Sao Ngày Xưa</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5056,7 +5054,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Ước Nguyện Trong Chuông: Hồi Kết</t>
+          <t>Điều Ước Trong Chuông: Đoạn Kết</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5126,7 +5124,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Interlude</t>
+          <t>Khúc Tạm Ngừng</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5196,7 +5194,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Chương III Act V</t>
+          <t>Chương III Hồi V</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5266,7 +5264,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Interlude</t>
+          <t>Khúc Tạm Ngừng</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5336,7 +5334,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Interlude</t>
+          <t>Khúc Tạm Ngừng</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5406,8 +5404,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-Dưới bầu trời đêm tan rã</t>
+          <t>Dưới Bầu Trời Đêm Tan Băng</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5547,7 +5544,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm vụ chính Chương III Act V "Ánh Sao Từ Ngày Xưa"</t>
+          <t>Hoàn thành Chương III Hồi V "Ánh Sao Từ Ngày Xưa" trong Nhiệm Vụ Chính</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5617,7 +5614,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Mở khóa 10 Persona Pinball trong "Star Bouncing"</t>
+          <t>Mở khóa 10 Bóng Cá Tính trong "Nhảy Sao"</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5757,7 +5754,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Hoàn thành Endless Galaxy Track 3 trong "Star Bouncing"</t>
+          <t>Hoàn thành Đường Đua Dải Ngân Hà Vô Tận 3 trong "Nhảy Sao"</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5827,7 +5824,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm vụ Phụ "Message Stranded in Shimmer"</t>
+          <t>Hoàn thành Nhiệm Vụ Phụ "Thông Điệp Mắc Kẹt Trong Ánh Lấp Lánh"</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5967,7 +5964,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Nâng cấp Trại Cơ sở lên Cấp 2</t>
+          <t>Nâng cấp Trại Chính lên Cấp 2</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -6037,7 +6034,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Complete the prerequisite tasks first</t>
+          <t>Hoàn thành các nhiệm vụ tiền đề trước đã</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6107,7 +6104,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Đạt 25% Progress Thám hiểm ở tất cả khu vực tại Roya Frostlands - Dimmr Plains</t>
+          <t>Đạt 25% Tiến Độ Thám Hiểm ở tất cả khu vực tại Roya Frostlands - Dimmr Plains</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6177,7 +6174,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Turn clockwise/counterclockwise</t>
+          <t>Xoay theo chiều kim đồng hồ/ngược chiều kim đồng hồ</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6247,7 +6244,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Dash</t>
+          <t>Tấn Công Nhanh</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6387,7 +6384,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>GM Island Domain entrance</t>
+          <t>LỐI VÀO LÃNH ĐỊA ĐẢO QUẢN TRỊ VIÊN</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6457,7 +6454,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Chaotic Juncture: Spark</t>
+          <t>Điểm Giao Thoa Hỗn Loạn: Tia Lửa</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6527,7 +6524,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Statue of the Crownless: Heart</t>
+          <t>Tượng Vô Vương: Trái Tim</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6597,7 +6594,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>The Grand Library</t>
+          <t>Thư Viện Lớn</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6667,7 +6664,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Statue of the Crownless</t>
+          <t>Tượng Vô Vương</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6737,7 +6734,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Misty Forest</t>
+          <t>Rừng Sương Mù</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6807,7 +6804,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Moonlit Groves</t>
+          <t>Khu Rừng Ánh Trăng</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6877,7 +6874,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Chaotic Juncture</t>
+          <t>Điểm Giao Thoa Hỗn Loạn</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6947,7 +6944,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Marigold Woods</t>
+          <t>Rừng Marigold</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7017,7 +7014,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Flaming Remnants</t>
+          <t>Tàn Dư Lửa Cháy</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7087,7 +7084,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Eroded Ruins</t>
+          <t>Tàn Tích Xói Mòn</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7157,7 +7154,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>The Grand Library</t>
+          <t>Thư Viện Lớn</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7227,7 +7224,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Training Decive</t>
+          <t>Thiết Bị Huấn Luyện</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7297,7 +7294,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Thăng Tiến Pha</t>
+          <t>Thăng Hoa Giai Đoạn</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7367,7 +7364,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Simulation Training</t>
+          <t>Huấn Luyện Mô Phỏng</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7437,7 +7434,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>CE test</t>
+          <t>Kiểm tra CE</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7507,7 +7504,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Training Projector</t>
+          <t>Máy Chiếu Huấn Luyện</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7577,7 +7574,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Perspective Bender</t>
+          <t>Kẻ Bẻ Cong Góc Nhìn</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7647,7 +7644,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Parallel Perception</t>
+          <t>Nhận Thức Song Song</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7717,7 +7714,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Phiên Bản Hoạt Động Thử Nghiệm Nhân Vật</t>
+          <t>Phiên Bản Hoạt Động Nhân Vật Thử Nghiệm</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7787,7 +7784,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Vực Sâu Cõi Ảo Ảnh</t>
+          <t>Vực Sâu Cõi Ảo</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7997,7 +7994,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Hang Ẩn</t>
+          <t>Hang Động Ẩn</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8067,7 +8064,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Puppet Factory</t>
+          <t>Nhà Máy Búp Bê</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8137,7 +8134,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Tempest Mephis AI test</t>
+          <t>Kiểm tra AI Mephis Bão Tố</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8207,7 +8204,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Boss test</t>
+          <t>Thử Nghiệm Đầu Sỏ</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8277,7 +8274,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>TD test only</t>
+          <t>Chỉ dùng để thử nghiệm TD</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8347,7 +8344,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Nấu luyện Hợp kim</t>
+          <t>Nấu Luyện Hợp Kim</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8417,7 +8414,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Alloy Smelt II</t>
+          <t>Nấu Luyện Hợp Kim II</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8487,7 +8484,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Overdash Club</t>
+          <t>Câu lạc bộ Bay vượt tốc</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8557,7 +8554,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Mặt Trăng Đã Phán Như Vậy</t>
+          <t>Lời Trăng Răn Dạy</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8627,7 +8624,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Plum Blossom Pole</t>
+          <t>Cột Mận Hoa</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8697,7 +8694,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Yumyum Haven</t>
+          <t>Thiên Đường Ẩm Thực</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8767,7 +8764,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Cửa hàng Pháo Hoa</t>
+          <t>Cửa hàng pháo hoa</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8837,7 +8834,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Swim, Gulpuff, Swim</t>
+          <t>Bơi đi, Gulpuff, bơi lên!</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -8907,7 +8904,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Puppet Theater</t>
+          <t>Nhà Hát Búp Bê</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -8977,7 +8974,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Hsin's Fortuity</t>
+          <t>May mắn của Hsin</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9047,7 +9044,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Fan Drawing Stall</t>
+          <t>Gian Hàng Tranh Người Hâm Mộ</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9117,7 +9114,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Riddle Twiddle</t>
+          <t>Câu Đố Lung Tung</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9187,7 +9184,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Moon Shooter</t>
+          <t>Bắn Trăng</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9257,7 +9254,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Loong Dance</t>
+          <t>Điệu Múa Rồng</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9327,7 +9324,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Overflowing Picture Book</t>
+          <t>Sách Tranh Tràn</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9397,7 +9394,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Dreaming Deep</t>
+          <t>Giấc Mơ Sâu Thẳm</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9467,7 +9464,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Steward's Supply Station</t>
+          <t>Trạm cung ứng của Quản gia</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9537,7 +9534,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Spacetrek Archive</t>
+          <t>Lưu Trữ Spacetrek</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9607,7 +9604,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Resonator Nursing Unit</t>
+          <t>Đơn Vị Điều Dưỡng Resonator</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9677,7 +9674,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Royan Market</t>
+          <t>Chợ Roya</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9747,7 +9744,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Culinary Station</t>
+          <t>Trạm Ẩm Thực</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -9817,7 +9814,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Synth Armament Crafting Bay</t>
+          <t>Xưởng Chế Tạo Vũ Khí Tổng Hợp</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -9887,7 +9884,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Kỹ năng Đỗ Xe Tự Động &amp; Chuyên môn Kỹ thuật</t>
+          <t>Tự động đỗ xe &amp; Kỹ thuật Xpertise</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -10027,7 +10024,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Cửa hàng Mũ Bạc</t>
+          <t>Cửa Hàng Mũ Bạc</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10097,7 +10094,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Septimont Sonance Casket Collector</t>
+          <t>Người Thu Thập Rương Sonance Septimont</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10237,7 +10234,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Tacet Field:  Riccioli Islands</t>
+          <t>Tổ Tacet: Quần đảo Riccioli</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10307,7 +10304,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Tacet Field: Beohr Waters</t>
+          <t>Tổ Tacet: Vùng biển Beohr</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10377,7 +10374,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Tacet Field: Mournfell Canyon</t>
+          <t>Tổ Tacet: Hẻm Núi Mournfell</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10447,7 +10444,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Tacet Field: Stagnant Run</t>
+          <t>Tổ Tacet: Dòng Chảy Trì Trệ</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10517,7 +10514,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Tacet Field: Mawburrow Desert</t>
+          <t>Tổ Tacet: Sa Mạc Mawburrow</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10587,7 +10584,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Tacet Field: Mount Gjallar</t>
+          <t>Tổ Tacet: Núi Gjallar</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10657,7 +10654,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Tacet Field: Frostlands Transit Port</t>
+          <t>Tổ Tacet: Cảng trung chuyển Frostlands</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10727,7 +10724,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Tacet Field: Solisia Landing</t>
+          <t>Tổ Tacet: Bãi Đáp Solisia</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -10797,7 +10794,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Fallen Grave Nightmare Nest</t>
+          <t>Tổ Ảo Mộng Mộ Đêm Sa Ngã</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -10867,7 +10864,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>The Wastelands Nightmare Nest</t>
+          <t>Tổ Ác Mộng Vùng Đất Hoang</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -10937,7 +10934,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Tideline Verge Nightmare Nest</t>
+          <t>Bờ Triều Đẫm Máu - Tổ Ảm Đạm</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11007,7 +11004,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Three Heroes' Crest: Nightmare Nest</t>
+          <t>Ba Huy Hiệu Anh Hùng: Tổ Ác Mộng</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11077,7 +11074,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Honami City Nightmare Nest</t>
+          <t>Tổ Tacet Ác Mộng Thành phố Honami</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11147,7 +11144,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Trophy Chest Area</t>
+          <t>Khu Vực Rương Cúp</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11217,7 +11214,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Nguyện tiếng vỗ tay chào đón bạn</t>
+          <t>Tháng Năm chào đón ngươi bằng những tràng pháo tay</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11287,7 +11284,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Giấc Mơ Kiếm Gỉ Sét</t>
+          <t>Giấc Mộng Kiếm Rỉ Sét</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11357,7 +11354,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Tất cả Silence Filled</t>
+          <t>Tất cả sự im lặng đã tràn ngập</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11427,7 +11424,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Rachel the Fishing Boat</t>
+          <t>Thuyền Câu Rachel</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11497,7 +11494,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Port of Riccioli Dock</t>
+          <t>Cảng Riccioli</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11567,7 +11564,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Helm Village Dock</t>
+          <t>Bến Tàu Làng Helm</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11637,7 +11634,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Serene Bay Dock</t>
+          <t>Bến Vịnh Thanh Bình</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -11707,7 +11704,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Reyes Ruins Dock</t>
+          <t>Bến Tàu Tàn Tích Reyes</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -11777,7 +11774,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Wonder Bubble tại Bến Port of Riccioli</t>
+          <t>Bong Bóng Kỳ Diệu ở Cảng Riccioli</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -11847,7 +11844,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Wonder Bubble ở Helm Village</t>
+          <t>Bong Bóng Kỳ Diệu ở Làng Helm</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -11917,7 +11914,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Wonder Bubble ở Serene Bay</t>
+          <t>Bong Bóng Kỳ Diệu ở Vịnh Thanh Bình</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -11987,7 +11984,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Wonder Bubble ở Reyes Ruins</t>
+          <t>Bong Bóng Kỳ Diệu ở Tàn Tích Reyes</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12057,7 +12054,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Shipwright Queequeg</t>
+          <t>Thợ đóng tàu Queequeg</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12127,7 +12124,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Bouton de Rose Shop</t>
+          <t>Cửa Hàng Bouton de Rose</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12197,7 +12194,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Port of Riccioli</t>
+          <t>Cảng Riccioli</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12267,7 +12264,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Drake's Island</t>
+          <t>Đảo Drake</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12337,7 +12334,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Thương nhân Di vật</t>
+          <t>Thương Nhân Di Vật</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12407,7 +12404,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Weapon Crafting</t>
+          <t>Chế Tạo Vũ Khí</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12477,7 +12474,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Synthesizer</t>
+          <t>Bộ tổng hợp</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12547,7 +12544,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Synthesizer</t>
+          <t>Bộ tổng hợp</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -12617,7 +12614,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Souvenir Cửa hàng</t>
+          <t>Cửa Hàng Lưu Niệm</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -12687,7 +12684,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Panhua Restaurant</t>
+          <t>Nhà hàng Panhua</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -12757,7 +12754,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Shifang Pharmacy</t>
+          <t>Dược Phẩm Shifang</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -12827,7 +12824,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Mahe's Grocery</t>
+          <t>Cửa Hàng Tạp Hóa Mahe</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -12967,7 +12964,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Tiger's Maw Ore</t>
+          <t>Quặng Hàm Hổ</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13037,7 +13034,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Tiger's Maw Stall</t>
+          <t>Gian Hàng Hàm Hổ</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13107,7 +13104,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Yibai Clinic</t>
+          <t>Phòng Khám Yibai</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13177,7 +13174,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Repaired Strings, Preserved Melodies</t>
+          <t>Dây đàn đã sửa, khúc nhạc còn nguyên</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13247,7 +13244,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>KU-Money Exchange</t>
+          <t>Sàn Giao Dịch KU-Money</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13387,7 +13384,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Averardo Bank Counter</t>
+          <t>Quầy Giao Dịch Ngân Hàng Averardo</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13457,7 +13454,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Rosemary's Apothecary</t>
+          <t>Hiệu Thuốc Của Rosemary</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13527,7 +13524,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Trattoria Margherita</t>
+          <t>Quán Trattoria Margherita</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -13597,7 +13594,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Stillwind Sundries</t>
+          <t>Cửa Hàng Stillwind</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -13667,7 +13664,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Burrata Bakery</t>
+          <t>Tiệm Bánh Burrata</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -13737,7 +13734,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Masked Reverie</t>
+          <t>Mộng Ảo Đeo Mặt Nạ</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -13807,7 +13804,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Teensy Weensy</t>
+          <t>Nhóc Tí Hon</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -13947,7 +13944,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Kho Lưu Trữ Giai Điệu</t>
+          <t>Lưu Trữ Giai Điệu</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14017,7 +14014,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Gladiator's Portrait</t>
+          <t>Chân Dung Đấu Sĩ</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14157,7 +14154,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Synthesizer</t>
+          <t>Bộ tổng hợp</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14227,7 +14224,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Tactical Hologram: Tempest Mephis</t>
+          <t>Hologram Chiến Thuật: Tempest Mephis</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14297,7 +14294,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Tactical Hologram: Impermanence Heron</t>
+          <t>Hologram Chiến Thuật: Impermanence Heron</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14367,7 +14364,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Tactical Hologram: Mourning Aix</t>
+          <t>Hologram Chiến Thuật: Mourning Aix</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14437,7 +14434,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Tactical Hologram: Feilian Beringal</t>
+          <t>Bản Hologram Chiến Thuật: Feilian Beringal</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -14507,7 +14504,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Tactical Hologram: Crownless</t>
+          <t>Bản Hologram Chiến Thuật: Crownless</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -14577,7 +14574,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Tactical Hologram: Inferno Rider</t>
+          <t>Hologram Chiến Thuật: Inferno Rider</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -14647,7 +14644,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Tactical Hologram: Phantom Pain</t>
+          <t>Hologram Chiến Thuật: Nỗi Đau Ảo Ảnh</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -14717,7 +14714,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Tactical Hologram: Synchronization</t>
+          <t>Hologram Chiến Thuật: Đồng Bộ Hóa</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -14787,7 +14784,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Tacet Field: Central Plains</t>
+          <t>Tổ Tacet: Central Plains</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -14857,7 +14854,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Tacet Field: Desorock Highland I</t>
+          <t>Tổ Tacet: Desorock Highland I</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -14927,7 +14924,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Tacet Field: Tiger's Maw</t>
+          <t>Tổ Tacet: Tiger's Maw</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -14997,7 +14994,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Tacet Field: Whining Aix's Mire</t>
+          <t>Tổ Tacet: Whining Aix's Mire</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15067,7 +15064,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Tacet Field: Port City of Guixu</t>
+          <t>Tổ Tacet: Port City of Guixu</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15137,7 +15134,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Tacet Field: Desorock Highland II</t>
+          <t>Tổ Tacet: Desorock Highland II</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15207,7 +15204,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Tacet Field: Dim Forest</t>
+          <t>Tổ Tacet: Dim Forest</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15277,7 +15274,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Tacet Field: Fagaceae Peninsula</t>
+          <t>Tổ Tacet: Bán đảo Fagaceae</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15347,7 +15344,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Tacet Field: Penitent's End</t>
+          <t>Tổ Tacet: Bờ Vực Sám Hối</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -16117,7 +16114,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Fallacy of Không Return</t>
+          <t>Ảo Tưởng Vô Hồi</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16187,7 +16184,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Medium Tacet Field: Weapon</t>
+          <t>Tổ Tacet Cỡ Trung: Vũ Khí</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16257,7 +16254,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Medium Tacet Field: Echo</t>
+          <t>Tổ Tacet Cỡ Trung: Echo</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16327,7 +16324,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Medium Tacet Field: Tacetite</t>
+          <t>Tổ Tacet Cỡ Trung: Tacetit</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -16397,7 +16394,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Medium Tacet Field: Substance</t>
+          <t>Tổ Tacet Cỡ Trung: Chất</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -16467,7 +16464,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Sagaci Springs</t>
+          <t>Suối Sagaci</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -16537,7 +16534,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Echo Challenge: Clang Bang</t>
+          <t>Thử Thách Tiếng Vọng: Clang Bang</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -16607,7 +16604,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Stone Lift</t>
+          <t>Nâng Đá</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -16677,7 +16674,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Echo Challenge: Clang Bang</t>
+          <t>Thử Thách Tiếng Vọng: Clang Bang</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -16747,7 +16744,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Lumiscale Construct</t>
+          <t>Cấu Trúc Vảy Quang</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -16817,7 +16814,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Echo Challenge: Clang Bang</t>
+          <t>Thử Thách Tiếng Vọng: Clang Bang</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -16887,7 +16884,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Stone Lift</t>
+          <t>Nâng Đá</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -16957,7 +16954,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Mighty Lightcrusher</t>
+          <t>Ánh Sáng Nghiền Nát Vĩ Đại</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17027,7 +17024,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Xian'ge</t>
+          <t>Hiên Ca</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17097,7 +17094,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Echo Challenge: Clang Bang</t>
+          <t>Thử Thách Tiếng Vọng: Clang Bang</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17237,7 +17234,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Seaside Ruins</t>
+          <t>Tàn Tích Bên Bờ Biển</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -17307,7 +17304,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Construct: Protective Scales</t>
+          <t>Cấu Trúc: Vảy Bảo Hộ</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -17377,7 +17374,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>By Moon's Grace</t>
+          <t>Nhờ Ân Huệ của Mặt Trăng</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -17447,7 +17444,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Entrance to the Base</t>
+          <t>Lối vào Căn cứ</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -17517,7 +17514,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Secret Room</t>
+          <t>Căn Phòng Bí Mật</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -17587,7 +17584,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Entrance to the Base</t>
+          <t>Lối vào Căn cứ</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -17657,7 +17654,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Hidden Entrance</t>
+          <t>Lối Vào Bí Mật</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -17727,7 +17724,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Hidden Entrance</t>
+          <t>Lối Vào Bí Mật</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -17797,7 +17794,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Hidden Entrance</t>
+          <t>Lối Vào Bí Mật</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -17867,7 +17864,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Hidden Entrance</t>
+          <t>Lối Vào Bí Mật</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -17937,7 +17934,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Hidden Entrance</t>
+          <t>Lối Vào Bí Mật</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18007,7 +18004,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Secret Entrance</t>
+          <t>Lối Vào Bí Mật</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18077,7 +18074,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Secret Entrance</t>
+          <t>Lối Vào Bí Mật</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18147,7 +18144,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Secret Entrance</t>
+          <t>Lối Vào Bí Mật</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -18217,7 +18214,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Secret Entrance</t>
+          <t>Lối Vào Bí Mật</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -18287,7 +18284,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Secret Entrance</t>
+          <t>Lối Vào Bí Mật</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -18357,7 +18354,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Secret Entrance</t>
+          <t>Lối Vào Bí Mật</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -18427,7 +18424,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Echo Station Entrance</t>
+          <t>Lối Vào Trạm Echo</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -18497,7 +18494,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Lối Vào Precious Metals and Artworks Depository</t>
+          <t>Lối vào Kho tàng Kim loại &amp; Tác phẩm Nghệ thuật</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -18567,7 +18564,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Echo Depository Entrance</t>
+          <t>Lối Vào Kho Lưu Trữ Tiếng Vọng</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -18637,7 +18634,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Underground Depository Entrance</t>
+          <t>Lối Vào Kho Lưu Trữ Dưới Lòng Đất</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -18707,7 +18704,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Secret Entrance</t>
+          <t>Lối Vào Bí Mật</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -18777,7 +18774,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Secret Entrance</t>
+          <t>Lối Vào Bí Mật</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -18847,7 +18844,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Echo Challenge: Dancer Hacking</t>
+          <t>Thử Thách Tiếng Vọng: Vũ Điệu Hacker</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -18917,7 +18914,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Sanctum of Quietude</t>
+          <t>Thánh Đường Tĩnh Lặng</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -18987,7 +18984,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Howlfang Lair</t>
+          <t>Sào Huyệt Howlfang</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19057,7 +19054,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Maroonwood Crypt</t>
+          <t>Mộ địa Maroonwood</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19127,7 +19124,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Maroonwood Maw</t>
+          <t>Hàm Thú Maroonwood</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -19197,7 +19194,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Corrosaurus's Throat</t>
+          <t>Họng Corrosaurus</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -19267,7 +19264,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Energy Hub Elevator</t>
+          <t>Thang Máy Trạm Năng Lượng</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -19337,7 +19334,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Rinascita-Averardo Vault-The Vault's Dock</t>
+          <t>Kho Tàng Rinascita-Averardo-Bến Đậu Của Kho</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -19407,7 +19404,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Rinascita-Averardo Vault</t>
+          <t>Kho Tàng Rinascita-Averardo</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -19477,7 +19474,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Rinascita-Averardo Vault</t>
+          <t>Kho Tàng Rinascita-Averardo</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -19547,7 +19544,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Rinascita-Averardo Vault</t>
+          <t>Kho Tàng Rinascita-Averardo</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -19617,7 +19614,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Rinascita-Fagaceae Peninsula</t>
+          <t>Bán Đảo Fagaceae-Rinascita</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -19687,7 +19684,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Rinascita-Fagaceae Peninsula-Oakheart Highcourt</t>
+          <t>Bán Đảo Fagaceae-Rinascita-Tòa Án Tối Cao Oakheart</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -19757,7 +19754,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Rinascita-Fagaceae Peninsula</t>
+          <t>Bán Đảo Fagaceae-Rinascita</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -19827,7 +19824,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Rinascita-Fagaceae Peninsula-Bãi Biển Hơi Thở Cuối</t>
+          <t>Bán Đảo Fagaceae-Rinascita-Bờ Biển Hơi Thở Cuối Cùng</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -19897,7 +19894,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Rinascita-Hallowed Reach</t>
+          <t>Rinascita-Vùng Đất Thiêng</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -19967,7 +19964,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Rinascita-Hallowed Reach</t>
+          <t>Rinascita-Vùng Đất Thiêng</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -20037,7 +20034,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Rinascita-Hallowed Reach-The Wailing Ascent</t>
+          <t>Rinascita-Vùng Đất Thiêng-Đỉnh Gió Than</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
@@ -20107,7 +20104,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Rinascita-Hallowed Reach-Requiem Ravine</t>
+          <t>Rinascita-Vùng Đất Thiêng-Khe Núi Ai Oán</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -20177,7 +20174,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Rinascita-Hallowed Reach-Requiem Ravine</t>
+          <t>Rinascita-Vùng Đất Thiêng-Khe Núi Ai Oán</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -20247,7 +20244,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Rinascita-Nimbus Sanctum-Mistveil Bay</t>
+          <t>Rinascita-Thánh Điện Nimbus-Vịnh Sương Mù</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -20317,7 +20314,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Rinascita-Nimbus Sanctum</t>
+          <t>Rinascita-Thánh Điện Nimbus</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -20387,7 +20384,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Rinascita-Nimbus Sanctum-Sảnh Phản Chiếu</t>
+          <t>Rinascita-Thánh Điện Nimbus-Sảnh Đường Suy Tư</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -20457,7 +20454,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Rinascita-Nimbus Sanctum</t>
+          <t>Rinascita-Thánh Điện Nimbus</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -20527,7 +20524,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Rinascita-Nimbus Sanctum-Garden Đã Mất</t>
+          <t>Rinascita-Thánh Điện Nimbus-Vườn Địa Đàng Lạc Lối</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -20597,7 +20594,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Rinascita-Nimbus Sanctum-Gold's Landing</t>
+          <t>Rinascita-Thánh Điện Nimbus-Bến Vàng</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -20667,7 +20664,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Rinascita-Penitent's End-Figurehead's Shrine</t>
+          <t>Rinascita-Ngõ Cầu Xin-Đền Thờ Hình Nhân</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
@@ -20737,7 +20734,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Rinascita-Penitent's End</t>
+          <t>Rinascita-Ngõ Cầu Xin</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -20807,7 +20804,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Rinascita-Penitent's End</t>
+          <t>Rinascita-Ngõ Cầu Xin</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
@@ -20877,7 +20874,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Rinascita-Penitent's End-The Strand</t>
+          <t>Rinascita - Kết Thúc của Kẻ Ăn Năn - Dải Bờ</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -20947,7 +20944,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Rinascita-Penitent's End-Fool's Elysium</t>
+          <t>Rinascita-Ngõ Cầu Xin-Thiên Đường Của Kẻ Ngốc</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
@@ -21017,7 +21014,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Rinascita-Penitent's End-Fool's Elysium</t>
+          <t>Rinascita-Ngõ Cầu Xin-Thiên Đường Của Kẻ Ngốc</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -21087,7 +21084,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Rinascita-Whisperwind Haven</t>
+          <t>Rinascita - Whisperwind Haven</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -21157,7 +21154,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Rinascita - Whisperwind Haven - Egla Town</t>
+          <t>Rinascita - Thung Lũng Gió Thì Thầm - Thị Trấn Egla</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
@@ -21227,7 +21224,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Rinascita-Whisperwind Haven</t>
+          <t>Rinascita - Whisperwind Haven</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -21297,7 +21294,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Rinascita-Whisperwind Haven</t>
+          <t>Rinascita - Whisperwind Haven</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -21367,7 +21364,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Rinascita-Whisperwind Haven-The Polyphemos Windmills</t>
+          <t>Rinascita - Whisperwind Haven - Cối Xay Gió Polyphemos</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
@@ -21437,7 +21434,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Rinascita-Whisperwind Haven</t>
+          <t>Rinascita - Whisperwind Haven</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
@@ -21507,7 +21504,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Rinascita-Whisperwind Haven-Silver Moon Grove</t>
+          <t>Rinascita - Whisperwind Haven - Rừng Trăng Bạc</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
@@ -21577,7 +21574,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Rinascita-Whisperwind Haven-Silver Moon Grove</t>
+          <t>Rinascita - Whisperwind Haven - Rừng Trăng Bạc</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -21647,7 +21644,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Rinascita-Ragunna City</t>
+          <t>Rinascita - Thành phố Ragunna</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -21717,7 +21714,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Rinascita-Thessaleo Fells-The Thorncrown Rises</t>
+          <t>Rinascita - Thessaleo Fells - Vùng Đất Gai Mọc</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -21787,7 +21784,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Rinascita-Thessaleo Fells</t>
+          <t>Rinascita - Thessaleo Fells</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -21857,7 +21854,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Rinascita-Thessaleo Fells-Twin Peaks</t>
+          <t>Rinascita - Thessaleo Fells - Song Phong</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
@@ -21927,7 +21924,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Rinascita-Thessaleo Fells-Porto-Veno Castle</t>
+          <t>Rinascita - Thessaleo Fells - Lâu Đài Porto-Veno</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -21997,7 +21994,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Rinascita-Thessaleo Fells-Twin Peaks</t>
+          <t>Rinascita - Thessaleo Fells - Song Phong</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -22067,7 +22064,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Rinascita-Ragunna-Island</t>
+          <t>Rinascita - Đảo Ragunna</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
@@ -22137,7 +22134,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Rinascita-Ragunna-City Center</t>
+          <t>Rinascita - Ragunna - Trung Tâm Thành Phố</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -22207,7 +22204,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Gondola Platform</t>
+          <t>Sân ga Gondola</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -22277,7 +22274,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Gondola Platform</t>
+          <t>Sân ga Gondola</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -22347,7 +22344,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Gondola Platform</t>
+          <t>Sân ga Gondola</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -22417,7 +22414,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Gondola Platform</t>
+          <t>Sân ga Gondola</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -22487,7 +22484,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Gondola Platform</t>
+          <t>Sân ga Gondola</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -22557,7 +22554,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Gondola Platform</t>
+          <t>Sân ga Gondola</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -22627,7 +22624,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Gondola Platform</t>
+          <t>Sân ga Gondola</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -22697,7 +22694,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Gondola Platform</t>
+          <t>Sân ga Gondola</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -22767,7 +22764,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Gondola Platform</t>
+          <t>Sân ga Gondola</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -22837,7 +22834,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Gondola Platform</t>
+          <t>Sân ga Gondola</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -22907,7 +22904,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Gondola Platform</t>
+          <t>Sân ga Gondola</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -22977,7 +22974,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Gondola Platform</t>
+          <t>Sân ga Gondola</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -23047,7 +23044,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Gondola Platform</t>
+          <t>Sân ga Gondola</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -23117,7 +23114,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Gondola Platform</t>
+          <t>Sân ga Gondola</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -23257,7 +23254,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Treasure Spot</t>
+          <t>Điểm Kho Báu</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -23327,7 +23324,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Thử thách Ba Anh Em Fratellis</t>
+          <t>Thử Thách Của Ba Anh Em Fratelli</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -23397,7 +23394,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Tactical Hologram: Vitreum Dancer</t>
+          <t>Hologram Chiến Thuật: Vũ Công Vitreum</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -23537,7 +23534,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>[Echo Challenge: Flight I]</t>
+          <t>[Thử Thách Tiếng Vọng: Bay Cấp I]</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -23607,7 +23604,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>[Echo Challenge: Flight VI]</t>
+          <t>Thử Thách Tiếng Vọng: Bay Cấp VI</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -23677,7 +23674,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>[Echo Challenge: Flight III]</t>
+          <t>[Thử Thách Tiếng Vọng: Bay Cấp III]</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
@@ -23747,7 +23744,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>[Echo Challenge: Flight IV]</t>
+          <t>[Thử Thách Tiếng Vọng: Bay Cấp IV]</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -23817,7 +23814,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>[Echo Challenge: Flight VII]</t>
+          <t>Thử Thách Tiếng Vọng: Bay Cấp VII</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -23887,7 +23884,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>[Echo Challenge: Flight V]</t>
+          <t>Thử Thách Tiếng Vọng: Bay Cấp V</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -23957,7 +23954,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>[Echo Challenge: Flight II]</t>
+          <t>[Thử Thách Tiếng Vọng: Bay Cấp II]</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -24027,7 +24024,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Echo Challenge: Flight</t>
+          <t>Thử Thách Tiếng Vọng: Bay Lượn</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
@@ -24097,7 +24094,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>[Echo Challenge: Flight I]</t>
+          <t>[Thử Thách Tiếng Vọng: Bay Cấp I]</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
@@ -24167,7 +24164,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>[Echo Challenge: Flight II]</t>
+          <t>[Thử Thách Tiếng Vọng: Bay Cấp II]</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -24237,7 +24234,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>[Echo Challenge: Flight III]</t>
+          <t>[Thử Thách Tiếng Vọng: Bay Cấp III]</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -24307,7 +24304,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Vượt Qua Giới Hạn - Sóng Dữ Dội</t>
+          <t>Vượt Qua Biên Giới - Sóng Dữ Dội</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -24377,7 +24374,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Những Khoảnh Khắc Tan Theo Gió</t>
+          <t>Khoảnh khắc bay theo gió</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -24447,7 +24444,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Gravity Calibrator</t>
+          <t>Bộ Điều Chỉnh Trọng Lực</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -24517,7 +24514,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Ace Wings</t>
+          <t>Đôi Cánh Phi Thường</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -24587,7 +24584,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>[Echo Challenge: Flight]</t>
+          <t>Thử Thách Tiếng Vọng: Bay</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
@@ -24657,7 +24654,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Boat Racing</t>
+          <t>Đua Thuyền</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
@@ -24727,7 +24724,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Flash Dodge</t>
+          <t>Né Tia Chớp</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -24797,7 +24794,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Echo Challenge: Gulpuff</t>
+          <t>Thử Thách Tiếng Vọng: Gulpuff</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
@@ -24867,7 +24864,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Cloud Platformer</t>
+          <t>Bậc Thang Mây</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
@@ -24937,7 +24934,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Traces of Tides I</t>
+          <t>Dấu vết của Thủy Triều I</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -25007,7 +25004,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Traces of Tides II</t>
+          <t>Dấu vết của Thủy Triều II</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -25077,7 +25074,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Traces of Tides III</t>
+          <t>Dấu vết của Thủy Triều III</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
@@ -25147,7 +25144,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Traces of Tides IV</t>
+          <t>Dấu vết của Thủy Triều IV</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -25217,7 +25214,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Traces of Tides V</t>
+          <t>Dấu Vết Thủy Triều V</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
@@ -25287,7 +25284,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Traces of Tides VI</t>
+          <t>Dấu Vết Thủy Triều VI</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
@@ -25357,7 +25354,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Traces of Tides VII</t>
+          <t>Dấu Vết Thủy Triều VII</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -25427,7 +25424,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Traces of Tides VIII</t>
+          <t>Dấu Vết Thủy Triều VIII</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -25497,7 +25494,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Memory Travelogue II</t>
+          <t>Hồi Ký Ký Ức II</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
@@ -25567,7 +25564,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Memory Travelogue III</t>
+          <t>Hồi Ký Ký Ức III</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -25637,7 +25634,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Memory Travelogue IV</t>
+          <t>Hồi Ký Ký Ức IV</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -25707,7 +25704,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Memory Travelogue V</t>
+          <t>Hồi Ký Ký Ức V</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
@@ -25777,7 +25774,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Memory Travelogue VI</t>
+          <t>Hồi Ký Ký Ức VI</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
@@ -25847,7 +25844,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Memory Travelogue VII</t>
+          <t>Hồi Ký Ký Ức VII</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
@@ -25917,7 +25914,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Memory Travelogue VIII</t>
+          <t>Hồi Ký Ký Ức VIII</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -25987,7 +25984,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Memory Travelogue IX</t>
+          <t>Hồi Ký Ký Ức IX</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -26057,7 +26054,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Memory Travelogue X</t>
+          <t>Hồi Ký Ký Ức X</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
@@ -26127,7 +26124,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Memory Travelogue XI</t>
+          <t>Hồi Ký Ký Ức XI</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -26197,7 +26194,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Memory Travelogue XII</t>
+          <t>Hồi Ký Ký Ức XII</t>
         </is>
       </c>
       <c r="N368" t="inlineStr">
@@ -26267,7 +26264,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Averardo Bank Counter</t>
+          <t>Quầy Giao Dịch Ngân Hàng Averardo</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -26337,7 +26334,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Waypoint</t>
+          <t>Điểm Dẫn Đường</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
@@ -26407,7 +26404,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Lootmapper</t>
+          <t>Bản Đồ Tài Nguyên</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -26477,7 +26474,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Overworld</t>
+          <t>Thế Giới Mở</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
@@ -26547,7 +26544,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Bãi Lầy Whining Aix</t>
+          <t>Whining Aix's Mire</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
@@ -26617,7 +26614,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Invisible Walls at Crownless combat</t>
+          <t>Bức Tường Vô Hình trong trận chiến Crownless</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
@@ -26687,7 +26684,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Tường vô hình gần dungeon 1 Dinh Thống Đốc</t>
+          <t>Tường vô hình gần dungeon Dinh Thống Đốc 1</t>
         </is>
       </c>
       <c r="N375" t="inlineStr">
@@ -26757,7 +26754,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Tường vô hình gần dungeon 2 Dinh Thống Đốc</t>
+          <t>Tường vô hình gần Dungeon 2 - Dinh Thống Đốc</t>
         </is>
       </c>
       <c r="N376" t="inlineStr">
@@ -26827,7 +26824,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Tường vô hình gần dungeon 3 Dinh Thống Đốc</t>
+          <t>Tường vô hình gần Dungeon 3 - Dinh Thống Đốc</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
@@ -26897,7 +26894,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Invisible Walls for one-time dungeon</t>
+          <t>Tường vô hình cho dungeon một lần</t>
         </is>
       </c>
       <c r="N378" t="inlineStr">
@@ -26967,7 +26964,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Tường vô hình gần dungeon 4 Dinh Thống Đốc</t>
+          <t>Tường vô hình gần Dungeon 4 - Dinh Thống Đốc</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
@@ -27037,7 +27034,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Lollo Warehouse</t>
+          <t>Kho hàng Lollo</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
@@ -27107,7 +27104,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Port Gunchao</t>
+          <t>Cảng Gunchao</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
@@ -27177,7 +27174,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Frosting Harbor</t>
+          <t>Bến Cảng Phủ Băng</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
@@ -27247,7 +27244,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Court of Savantae Ruins</t>
+          <t>Tàn Tích Tòa Savantae</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
@@ -27317,7 +27314,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Waving Battlefield</t>
+          <t>Chiến Trường Gợn Sóng</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -27387,7 +27384,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Plateau Ruins</t>
+          <t>Tàn Tích Cao Nguyên</t>
         </is>
       </c>
       <c r="N385" t="inlineStr">
@@ -27457,7 +27454,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Heron Wetland</t>
+          <t>Đầm Lầy Heron</t>
         </is>
       </c>
       <c r="N386" t="inlineStr">
@@ -27527,7 +27524,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Vùng kích hoạt đầu tiên trong Nhiệm vụ Main</t>
+          <t>Vùng kích hoạt đầu tiên của Nhiệm Vụ Chính</t>
         </is>
       </c>
       <c r="N387" t="inlineStr">
@@ -27597,7 +27594,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Vùng kích hoạt thứ hai trong Nhiệm vụ Main</t>
+          <t>Vùng kích hoạt thứ hai trong Nhiệm Vụ Chính</t>
         </is>
       </c>
       <c r="N388" t="inlineStr">
@@ -27667,7 +27664,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Wall vô hình cho Hướng dẫn tại Gorges of Spirits 1</t>
+          <t>Bức Tường Vô Hình hướng dẫn ở Gorges of Spirits 1</t>
         </is>
       </c>
       <c r="N389" t="inlineStr">
@@ -27737,7 +27734,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Wall vô hình cho Hướng dẫn tại Gorges of Spirits 5</t>
+          <t>Bức Tường Vô Hình hướng dẫn ở Gorges of Spirits 5</t>
         </is>
       </c>
       <c r="N390" t="inlineStr">
@@ -27807,7 +27804,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Wall vô hình cho Hướng dẫn tại Gorges of Spirits 8</t>
+          <t>Bức Tường Vô Hình hướng dẫn ở Gorges of Spirits 8</t>
         </is>
       </c>
       <c r="N391" t="inlineStr">
@@ -27877,7 +27874,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Abandoned Subway Station</t>
+          <t>Ga Tàu Điện Ngầm Bị Bỏ Rơi</t>
         </is>
       </c>
       <c r="N392" t="inlineStr">
@@ -28017,7 +28014,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Tethys' Deep</t>
+          <t>Sâu Thẳm của Tethys</t>
         </is>
       </c>
       <c r="N394" t="inlineStr">
@@ -28087,7 +28084,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>TD Observatory</t>
+          <t>Đài Quan Sát</t>
         </is>
       </c>
       <c r="N395" t="inlineStr">
@@ -28157,7 +28154,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Tethys Hub</t>
+          <t>Trung Tâm Tethys</t>
         </is>
       </c>
       <c r="N396" t="inlineStr">
@@ -28227,7 +28224,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Haven of Sprouts</t>
+          <t>Mầm Xanh Thịnh Vượng</t>
         </is>
       </c>
       <c r="N397" t="inlineStr">
@@ -28367,7 +28364,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Data Torrent</t>
+          <t>Dòng Dữ liệu</t>
         </is>
       </c>
       <c r="N399" t="inlineStr">
@@ -28437,7 +28434,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Modulation Hall</t>
+          <t>Đại Sảnh Điều Tần</t>
         </is>
       </c>
       <c r="N400" t="inlineStr">
@@ -28507,7 +28504,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Energy Hub</t>
+          <t>Trung Tâm Năng Lượng</t>
         </is>
       </c>
       <c r="N401" t="inlineStr">
@@ -28577,7 +28574,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Error Cell</t>
+          <t>Tế Bào Lỗi</t>
         </is>
       </c>
       <c r="N402" t="inlineStr">
@@ -28647,7 +28644,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Bank of Life</t>
+          <t>Ngân Hàng Sự Sống</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -28717,7 +28714,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Mysterious Room</t>
+          <t>Căn Phòng Bí Ẩn</t>
         </is>
       </c>
       <c r="N404" t="inlineStr">
@@ -28787,7 +28784,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Error Cell Sublevel 1</t>
+          <t>Hầm Dưới Tầng 1 Tế Bào Lỗi</t>
         </is>
       </c>
       <c r="N405" t="inlineStr">
@@ -28857,7 +28854,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Error Cell Floor 1</t>
+          <t>Tầng 1 Tế Bào Lỗi</t>
         </is>
       </c>
       <c r="N406" t="inlineStr">
@@ -28927,7 +28924,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Bank of Life Floor 1</t>
+          <t>Tầng 1 Ngân Hàng Sự Sống</t>
         </is>
       </c>
       <c r="N407" t="inlineStr">
@@ -28997,7 +28994,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Bank of Life Floor 2</t>
+          <t>Tầng 2 Ngân Hàng Sự Sống</t>
         </is>
       </c>
       <c r="N408" t="inlineStr">
@@ -29137,7 +29134,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Gold's Landing</t>
+          <t>Bến Đáp Vàng</t>
         </is>
       </c>
       <c r="N410" t="inlineStr">
@@ -29207,7 +29204,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Dolomites Broken Bridge</t>
+          <t>Cầu Gãy Dolomites</t>
         </is>
       </c>
       <c r="N411" t="inlineStr">
@@ -29277,7 +29274,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Fool's Elysium</t>
+          <t>Thiên Đường Ngu Ngốc</t>
         </is>
       </c>
       <c r="N412" t="inlineStr">
@@ -29347,7 +29344,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Figurehead's Shrine</t>
+          <t>Đền Thờ Bù Nhìn</t>
         </is>
       </c>
       <c r="N413" t="inlineStr">
@@ -29417,7 +29414,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Wailing Ascent</t>
+          <t>Bước Thăng Hoa Than Khóc</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -29487,7 +29484,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>The Strand</t>
+          <t>Dòng Tacet</t>
         </is>
       </c>
       <c r="N415" t="inlineStr">
@@ -29557,7 +29554,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Iridescent Hollow</t>
+          <t>Hốm Irideglow</t>
         </is>
       </c>
       <c r="N416" t="inlineStr">
@@ -29627,7 +29624,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Requiem Ravine</t>
+          <t>Hẻm Núi Khúc Ca</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
@@ -29697,7 +29694,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Hallowed Reach: Underground</t>
+          <t>Thánh Vực: Dưới Lòng Đất</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -29767,7 +29764,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Silver Moon Grove</t>
+          <t>Lâm Nguyệt Bạc</t>
         </is>
       </c>
       <c r="N419" t="inlineStr">
@@ -29837,7 +29834,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Polyphemos Windmills</t>
+          <t>Cối Xay Gió Polyphemos</t>
         </is>
       </c>
       <c r="N420" t="inlineStr">
@@ -29907,7 +29904,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Mistveil Bay</t>
+          <t>Vịnh Mistveil</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -29977,7 +29974,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Egla Town</t>
+          <t>Thị Trấn Egla</t>
         </is>
       </c>
       <c r="N422" t="inlineStr">
@@ -30047,7 +30044,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Sunken Ideals: Ruins</t>
+          <t>Lý Tưởng Chìm: Tàn Tích</t>
         </is>
       </c>
       <c r="N423" t="inlineStr">
@@ -30117,7 +30114,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Fractured Cavern</t>
+          <t>Hang Động Nứt Gãy</t>
         </is>
       </c>
       <c r="N424" t="inlineStr">
@@ -30187,7 +30184,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Đại sảnh Phản chiếu</t>
+          <t>Đại Sảnh Phản Chiếu</t>
         </is>
       </c>
       <c r="N425" t="inlineStr">
@@ -30257,7 +30254,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Mistveil Bay</t>
+          <t>Vịnh Mistveil</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
@@ -30327,7 +30324,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Gold's Landing</t>
+          <t>Bến Đáp Vàng</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -30397,7 +30394,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Oakheart Highcourt</t>
+          <t>Tòa Thượng Nghị Oakheart</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
@@ -30467,7 +30464,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Coast of Anticipation</t>
+          <t>Bờ Biển Chờ Đợi</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
@@ -30537,7 +30534,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Bờ biển Hơi Thở Cuối</t>
+          <t>Bờ Biển Hơi Thở Cuối Cùng</t>
         </is>
       </c>
       <c r="N430" t="inlineStr">
@@ -30607,7 +30604,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Oakheart Highcourt: Lower Tier</t>
+          <t>Tòa Thượng Nghị Oakheart: Tầng Dưới</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -30747,7 +30744,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Twin Peaks</t>
+          <t>Song Đỉnh</t>
         </is>
       </c>
       <c r="N433" t="inlineStr">
@@ -30887,7 +30884,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Garden của Kẻ Lạc Lối</t>
+          <t>Vườn của Kẻ Lạc Lối</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -30957,7 +30954,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>City Square</t>
+          <t>Quảng Trường Thành Phố</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
@@ -31027,7 +31024,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Bank Street</t>
+          <t>Phố Ngân Hàng</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -31097,7 +31094,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Giáo Đoàn Vực Sâu</t>
+          <t>Lệnh của Vực Sâu</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
@@ -31167,7 +31164,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Montelli Quarter</t>
+          <t>Khu Montelli</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
@@ -31237,7 +31234,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Đồi Hoàng Hôn</t>
+          <t>Thăng Bình Hoàng Hôn</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -31307,7 +31304,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Đồi Tiếng Vang</t>
+          <t>Sự Trỗi Dậy Vang Dội</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -31377,7 +31374,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Đồi Chỉ Huy</t>
+          <t>Lệnh Triệu Hồi</t>
         </is>
       </c>
       <c r="N442" t="inlineStr">
@@ -31447,7 +31444,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Wall vô hình cho Hướng dẫn tại Gorges of Spirits 9</t>
+          <t>Bức Tường Vô Hình hướng dẫn ở Gorges of Spirits 9</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -31517,7 +31514,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Wall vô hình ở đáy thang máy Jinzhou</t>
+          <t>Bức Tường Vô Hình dưới chân thang máy Jinzhou</t>
         </is>
       </c>
       <c r="N444" t="inlineStr">
@@ -31657,7 +31654,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Wall vô hình ở đỉnh thang máy Jinzhou</t>
+          <t>Bức Tường Vô Hình trên đỉnh thang máy Jinzhou</t>
         </is>
       </c>
       <c r="N446" t="inlineStr">
@@ -31727,7 +31724,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Tường vô hình cho dungeon Tower of Adversity luân hồi 1</t>
+          <t>Tường vô hình cho dungeon Tháp Nghịch Cảnh lặp 1</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -31797,7 +31794,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Tường vô hình cho dungeon Tower of Adversity luân hồi 2</t>
+          <t>Tường vô hình cho dungeon Tháp Nghịch Cảnh lặp 2</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -31867,7 +31864,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Tường vô hình cho dungeon Bản demo Linyang</t>
+          <t>Tường vô hình cho dungeon demo Linyang</t>
         </is>
       </c>
       <c r="N449" t="inlineStr">
@@ -31937,7 +31934,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Sky Ray</t>
+          <t>Tia Sét Trời</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -32007,7 +32004,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Dust-Sealed Track</t>
+          <t>Dấu Vết Bị Phong Ấn Bởi Bụi</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -32077,7 +32074,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Tiger's Maw Mine</t>
+          <t>Mỏ Hầm Hổ</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -32147,7 +32144,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Distribution Center</t>
+          <t>Trung Tâm Phân Phối</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -32217,7 +32214,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Tường vô hình cho kẻ địch tại Huanglong National Geographic</t>
+          <t>Tường vô hình cho kẻ địch ở Huanglong National Geographic</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -32287,7 +32284,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Tường vô hình cho nhiệm vụ nhân vật Jiyan</t>
+          <t>Bức Tường Vô Hình nhiệm vụ nhân vật Jiyan</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -32357,7 +32354,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Tường vô hình cho khu vực hạn chế trong Chương I và II @ Nhiệm vụ chính</t>
+          <t>Tường vô hình cho khu vực hạn chế trong Chương I và II@ Nhiệm vụ chính</t>
         </is>
       </c>
       <c r="N456" t="inlineStr">
@@ -32427,7 +32424,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Tường vô hình cho nhiệm vụ nhân vật Jiyan</t>
+          <t>Bức Tường Vô Hình nhiệm vụ nhân vật Jiyan</t>
         </is>
       </c>
       <c r="N457" t="inlineStr">
@@ -32567,7 +32564,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Tường vô hình cho combat nhiệm vụ tại Norfall Barrens</t>
+          <t>Tường vô hình cho chiến đấu trong nhiệm vụ Norfall Barrens</t>
         </is>
       </c>
       <c r="N459" t="inlineStr">
@@ -32637,7 +32634,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Tường vô hình cho combat nhiệm vụ tại Norfall Barrens</t>
+          <t>Tường vô hình cho chiến đấu trong nhiệm vụ Norfall Barrens</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -32707,7 +32704,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Tường vô hình cho combat nhiệm vụ tại Norfall Barrens</t>
+          <t>Tường vô hình cho chiến đấu trong nhiệm vụ Norfall Barrens</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -32777,7 +32774,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Tường vô hình cho combat nhiệm vụ tại Norfall Barrens</t>
+          <t>Tường vô hình cho chiến đấu trong nhiệm vụ Norfall Barrens</t>
         </is>
       </c>
       <c r="N462" t="inlineStr">
@@ -32847,7 +32844,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Tường vô hình cho combat nhiệm vụ tại Norfall Barrens</t>
+          <t>Tường vô hình cho chiến đấu trong nhiệm vụ Norfall Barrens</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -32917,7 +32914,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Tường vô hình cho nhiệm vụ tại Norfall Barrens</t>
+          <t>Tường vô hình cho nhiệm vụ Norfall Barrens</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -32987,7 +32984,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Tường vô hình cho nhiệm vụ tại Norfall Barrens</t>
+          <t>Tường vô hình cho nhiệm vụ Norfall Barrens</t>
         </is>
       </c>
       <c r="N465" t="inlineStr">
@@ -33127,7 +33124,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Norfall Valley</t>
+          <t>Thung Lũng Norfall</t>
         </is>
       </c>
       <c r="N467" t="inlineStr">
@@ -33197,7 +33194,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Suspended Ruins</t>
+          <t>Tàn Tích Lơ Lửng</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -33267,7 +33264,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Tường vô hình trong quá trình tại Norfall Barrens</t>
+          <t>Tường vô hình trong quá trình Norfall Barrens</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -33337,7 +33334,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Tường vô hình cho nhiệm vụ phụ của Jiyan</t>
+          <t>Bức Tường Vô Hình nhiệm vụ phụ Jiyan</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33407,7 +33404,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Tường vô hình cho nhiệm vụ phụ của Jiyan</t>
+          <t>Bức Tường Vô Hình nhiệm vụ phụ Jiyan</t>
         </is>
       </c>
       <c r="N471" t="inlineStr">
@@ -33477,7 +33474,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Tường vô hình cho nhiệm vụ phụ của Jiyan</t>
+          <t>Bức Tường Vô Hình nhiệm vụ phụ Jiyan</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -33547,7 +33544,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Tường vô hình cho nhiệm vụ phụ của Jiyan</t>
+          <t>Bức Tường Vô Hình nhiệm vụ phụ Jiyan</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
@@ -33617,7 +33614,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Tường vô hình cho nhiệm vụ phụ của Jiyan</t>
+          <t>Bức Tường Vô Hình nhiệm vụ phụ Jiyan</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -33687,7 +33684,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Tường vô hình cho nhiệm vụ phụ của Jiyan</t>
+          <t>Bức Tường Vô Hình nhiệm vụ phụ Jiyan</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -33757,7 +33754,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Tường vô hình cho nhiệm vụ phụ của Jiyan</t>
+          <t>Bức Tường Vô Hình nhiệm vụ phụ Jiyan</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -33827,7 +33824,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Tường vô hình cho nhiệm vụ phụ của Jiyan</t>
+          <t>Bức Tường Vô Hình nhiệm vụ phụ Jiyan</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -33897,7 +33894,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Tường vô hình cho nhiệm vụ phụ của Jiyan</t>
+          <t>Bức Tường Vô Hình nhiệm vụ phụ Jiyan</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -33967,7 +33964,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Tường vô hình cho nhiệm vụ phụ của Jiyan</t>
+          <t>Bức Tường Vô Hình nhiệm vụ phụ Jiyan</t>
         </is>
       </c>
       <c r="N479" t="inlineStr">
@@ -34037,7 +34034,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Tường vô hình cho nhiệm vụ phụ của Jiyan</t>
+          <t>Bức Tường Vô Hình nhiệm vụ phụ Jiyan</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
@@ -34107,7 +34104,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Tường vô hình cho trường hợp test TD</t>
+          <t>Tường vô hình cho trường hợp thử nghiệm TD</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -34177,7 +34174,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>93-Tường vô hình cho trường hợp test TD</t>
+          <t>93-Tường Vô Hình cho trường hợp thử nghiệm TD</t>
         </is>
       </c>
       <c r="N482" t="inlineStr">
@@ -34247,7 +34244,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Tường vô hình cho nhiệm vụ nhân vật của Yangyang</t>
+          <t>Tường vô hình cho nhiệm vụ nhân vật Yangyang</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
@@ -34317,7 +34314,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Hẻm Núi Linh Hồn</t>
+          <t>Gorges of Spirits</t>
         </is>
       </c>
       <c r="N484" t="inlineStr">
@@ -34387,7 +34384,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Bell-Borne Ravine</t>
+          <t>Khe Núi Bell-Borne</t>
         </is>
       </c>
       <c r="N485" t="inlineStr">
@@ -34457,7 +34454,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Memento Square</t>
+          <t>Quảng Trường Kỷ Vật</t>
         </is>
       </c>
       <c r="N486" t="inlineStr">
@@ -34527,7 +34524,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Clouded Cliffs</t>
+          <t>Vách Đá Mây Mù</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -34737,7 +34734,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Lake Heights</t>
+          <t>Cao Nguyên Hồ</t>
         </is>
       </c>
       <c r="N490" t="inlineStr">
@@ -34807,7 +34804,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Shade Ridge</t>
+          <t>Vách Bóng Tối</t>
         </is>
       </c>
       <c r="N491" t="inlineStr">
@@ -34877,7 +34874,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Đồng bằng Trung tâm</t>
+          <t>Central Plains</t>
         </is>
       </c>
       <c r="N492" t="inlineStr">
@@ -34947,7 +34944,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Tiderise Cliff</t>
+          <t>Vách Đá Triều Dâng</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
@@ -35017,7 +35014,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Stone Pile Plain</t>
+          <t>Đồng Bằng Đống Đá</t>
         </is>
       </c>
       <c r="N494" t="inlineStr">
@@ -35087,7 +35084,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Gubei Pass</t>
+          <t>Ải Cổ Bối</t>
         </is>
       </c>
       <c r="N495" t="inlineStr">
@@ -35157,7 +35154,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Qichi Village</t>
+          <t>Làng Qichi</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
@@ -35227,7 +35224,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Loong's Gaze Suburbs</t>
+          <t>Ngoại Ô Ánh Mắt Rồng</t>
         </is>
       </c>
       <c r="N497" t="inlineStr">
@@ -35297,7 +35294,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Taoyuan Vale</t>
+          <t>Thung Lũng Đào Nguyên</t>
         </is>
       </c>
       <c r="N498" t="inlineStr">
@@ -35367,7 +35364,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Xiehua Village</t>
+          <t>Làng Tạ Hoa</t>
         </is>
       </c>
       <c r="N499" t="inlineStr">
@@ -35437,7 +35434,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Fireflies Sea</t>
+          <t>Biển Đom Đóm Lửa</t>
         </is>
       </c>
       <c r="N500" t="inlineStr">
@@ -35507,7 +35504,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Cao nguyên Desorock</t>
+          <t>Desorock Highland</t>
         </is>
       </c>
       <c r="N501" t="inlineStr">
